--- a/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
+++ b/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T22:33:34+00:00</t>
+    <t>2026-02-04T13:10:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
+++ b/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:10:34+00:00</t>
+    <t>2026-02-04T15:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
+++ b/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:12:10+00:00</t>
+    <t>2026-02-04T18:47:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
+++ b/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T21:49:31+00:00</t>
+    <t>2026-02-04T22:45:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
+++ b/sitepreview/trust/v1.4.0/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T22:45:13+00:00</t>
+    <t>2026-02-04T23:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
